--- a/checkrates/week-19/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-19/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1331,14 +1331,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2C · BKGS&gt;0 · peor Eficacia · ordenado ↑</t>
+          <t>B2C · BKGS&gt;0 · peor Eficacia · ordenado por Eficacia ↑ (menor primero)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6798,18 +6798,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6829,7 +6830,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6846,35 +6847,40 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -6889,27 +6895,32 @@
           <t>Hilton</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, HBSI, Internal</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>73567</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>66833</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.9084643930022972</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.0003126401783408322</v>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6924,27 +6935,32 @@
           <t>Hyatt</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>48369</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>46030</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.9516425809919576</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.001426533523537803</v>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6959,27 +6975,32 @@
           <t>IHG</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>43028</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>42216</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.9811285674444548</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.000209166124384122</v>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6994,27 +7015,32 @@
           <t>AA-Independent</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, HBSI, Internal, Siteminder, SynXis, Travelclick</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>20615</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>19290</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>428</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.9357264128062091</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.02076158137278681</v>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -7029,27 +7055,32 @@
           <t>Accor</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>12861</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>12217</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.9499261332711297</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.001321825674519866</v>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7064,27 +7095,32 @@
           <t>Wyndham</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>11295</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>10547</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.93377600708278</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.001505090748118637</v>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7099,27 +7135,32 @@
           <t>Caesars Entertainment</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>8394</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="E12" s="12" t="n">
         <v>6296</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.7500595663569216</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.002859185132237312</v>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7134,27 +7175,32 @@
           <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>4162</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>4156</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="G13" s="13" t="n">
         <v>0.9985583853916387</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.003844305622296973</v>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7169,27 +7215,32 @@
           <t>Disney</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>3453</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>3416</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="G14" s="13" t="n">
         <v>0.9892846799884158</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.01013611352447147</v>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7204,27 +7255,32 @@
           <t>MGM Resorts</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>3051</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>2962</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="G15" s="13" t="n">
         <v>0.970829236315962</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.0006555227794165847</v>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7239,27 +7295,32 @@
           <t>Best Western</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, SynXis</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
         <v>2890</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>2811</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="G16" s="13" t="n">
         <v>0.9726643598615917</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7274,27 +7335,32 @@
           <t>Universal</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>2117</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>1681</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="G17" s="13" t="n">
         <v>0.7940481813887577</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.005668398677373642</v>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7309,27 +7375,32 @@
           <t>CHOICE</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>1676</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>1616</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="G18" s="13" t="n">
         <v>0.964200477326969</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.01312649164677804</v>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7344,27 +7415,32 @@
           <t>Barcelo</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
         <v>1608</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="E19" s="12" t="n">
         <v>1531</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="G19" s="13" t="n">
         <v>0.9521144278606966</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.001865671641791045</v>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7379,27 +7455,32 @@
           <t>PAM Hotels</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Internal, SynXis</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n">
         <v>1017</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="E20" s="12" t="n">
         <v>1005</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="G20" s="13" t="n">
         <v>0.9882005899705014</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.005899705014749262</v>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7414,27 +7495,32 @@
           <t>Camino Real</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Travelclick</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>975</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="E21" s="12" t="n">
         <v>974</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="G21" s="13" t="n">
         <v>0.9989743589743589</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.06974358974358974</v>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -7449,27 +7535,32 @@
           <t>Presidente Intercontinental</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>841</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>713</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="G22" s="13" t="n">
         <v>0.8478002378121284</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7484,27 +7575,32 @@
           <t>Wynn Las Vegas</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>753</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="E23" s="12" t="n">
         <v>751</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="G23" s="13" t="n">
         <v>0.9973439575033201</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.006640106241699867</v>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7519,27 +7615,32 @@
           <t>GRUPO POSADAS</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>747</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="E24" s="12" t="n">
         <v>722</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="G24" s="13" t="n">
         <v>0.9665327978580991</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.008032128514056224</v>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7554,27 +7655,32 @@
           <t>Hoteles Geh Suites</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>743</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="E25" s="12" t="n">
         <v>720</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="G25" s="13" t="n">
         <v>0.9690444145356663</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.0107671601615074</v>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7589,27 +7695,32 @@
           <t>Decameron</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>693</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="E26" s="12" t="n">
         <v>598</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="G26" s="13" t="n">
         <v>0.862914862914863</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.001443001443001443</v>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7624,27 +7735,32 @@
           <t>Oasis</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
-        <v>551</v>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D27" s="12" t="n">
         <v>551</v>
       </c>
       <c r="E27" s="12" t="n">
+        <v>551</v>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="G27" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.003629764065335753</v>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7659,27 +7775,32 @@
           <t>Americas Hotels Group</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>481</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="E28" s="12" t="n">
         <v>465</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="G28" s="13" t="n">
         <v>0.9667359667359667</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.03534303534303534</v>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -7694,27 +7815,32 @@
           <t>Emporio</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
         <v>478</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="E29" s="12" t="n">
         <v>476</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="G29" s="13" t="n">
         <v>0.99581589958159</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.006276150627615063</v>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7729,27 +7855,32 @@
           <t>Marriott</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Omnibees</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
         <v>475</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="E30" s="12" t="n">
         <v>468</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="G30" s="13" t="n">
         <v>0.9852631578947368</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.008421052631578947</v>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7764,27 +7895,32 @@
           <t>Mision</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n">
-        <v>450</v>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D31" s="12" t="n">
         <v>450</v>
       </c>
       <c r="E31" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="G31" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.04666666666666667</v>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -7799,27 +7935,32 @@
           <t>Park Royal</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="n">
         <v>431</v>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="E32" s="12" t="n">
         <v>422</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="G32" s="13" t="n">
         <v>0.9791183294663574</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.004640371229698376</v>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7834,27 +7975,32 @@
           <t>Dann</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n">
-        <v>410</v>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D33" s="12" t="n">
         <v>410</v>
       </c>
       <c r="E33" s="12" t="n">
+        <v>410</v>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="G33" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7869,27 +8015,32 @@
           <t>Hoteles Movich</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
-        <v>408</v>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D34" s="12" t="n">
         <v>408</v>
       </c>
       <c r="E34" s="12" t="n">
+        <v>408</v>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="G34" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -7904,27 +8055,32 @@
           <t>Iberostar</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>HBSI, Internal</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
         <v>345</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="E35" s="12" t="n">
         <v>224</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="G35" s="13" t="n">
         <v>0.6492753623188405</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.03188405797101449</v>
       </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -7939,27 +8095,32 @@
           <t>EM Hotels</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
-        <v>318</v>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D36" s="12" t="n">
         <v>318</v>
       </c>
       <c r="E36" s="12" t="n">
+        <v>318</v>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="G36" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7974,27 +8135,32 @@
           <t>Hoteles Xcaret</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
-        <v>314</v>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D37" s="12" t="n">
         <v>314</v>
       </c>
       <c r="E37" s="12" t="n">
+        <v>314</v>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="13" t="n">
+      <c r="G37" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8009,27 +8175,32 @@
           <t>Melia</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>311</v>
-      </c>
-      <c r="D38" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="13" t="n">
+      <c r="F38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8044,27 +8215,32 @@
           <t>Karisma</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
         <v>305</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="E39" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="G39" s="13" t="n">
         <v>0.940983606557377</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.006557377049180328</v>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8079,27 +8255,32 @@
           <t>Ocean by H10</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
-        <v>277</v>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D40" s="12" t="n">
         <v>277</v>
       </c>
       <c r="E40" s="12" t="n">
+        <v>277</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="G40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.003610108303249098</v>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8114,27 +8295,32 @@
           <t>Sandos</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n">
-        <v>273</v>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D41" s="12" t="n">
         <v>273</v>
       </c>
       <c r="E41" s="12" t="n">
+        <v>273</v>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="G41" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8149,27 +8335,32 @@
           <t>Palladium Hotel Group</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n">
-        <v>257</v>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D42" s="12" t="n">
         <v>257</v>
       </c>
       <c r="E42" s="12" t="n">
+        <v>257</v>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F42" s="13" t="n">
+      <c r="G42" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.03891050583657588</v>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8184,27 +8375,32 @@
           <t>Bahia Principe</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>241</v>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="E43" s="12" t="n">
         <v>239</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="G43" s="13" t="n">
         <v>0.991701244813278</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8219,27 +8415,32 @@
           <t>GHL</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
-        <v>241</v>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D44" s="12" t="n">
         <v>241</v>
       </c>
       <c r="E44" s="12" t="n">
+        <v>241</v>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="13" t="n">
+      <c r="G44" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.004149377593360996</v>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8254,27 +8455,32 @@
           <t>Oxo Hotel</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
         <v>241</v>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="E45" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F45" s="13" t="n">
+      <c r="G45" s="13" t="n">
         <v>0.995850622406639</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.02489626556016597</v>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8289,27 +8495,32 @@
           <t>Faranda Hotels</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="E46" s="12" t="n">
         <v>237</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="13" t="n">
+      <c r="G46" s="13" t="n">
         <v>0.9875</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.008333333333333333</v>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8324,27 +8535,32 @@
           <t>Dorado Plaza</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n">
-        <v>217</v>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D47" s="12" t="n">
         <v>217</v>
       </c>
       <c r="E47" s="12" t="n">
+        <v>217</v>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="13" t="n">
+      <c r="G47" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.009216589861751152</v>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8359,27 +8575,32 @@
           <t>Krystal</t>
         </is>
       </c>
-      <c r="C48" s="12" t="n">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="n">
         <v>209</v>
       </c>
-      <c r="D48" s="12" t="n">
+      <c r="E48" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="G48" s="13" t="n">
         <v>0.01435406698564593</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8394,27 +8615,32 @@
           <t>BH Hoteles</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n">
-        <v>187</v>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D49" s="12" t="n">
         <v>187</v>
       </c>
       <c r="E49" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F49" s="13" t="n">
+      <c r="G49" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0.0267379679144385</v>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8429,27 +8655,32 @@
           <t>Alsol</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="D50" s="12" t="n">
+      <c r="E50" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="G50" s="13" t="n">
         <v>0.3983050847457627</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8464,27 +8695,32 @@
           <t>Grupo Welcome</t>
         </is>
       </c>
-      <c r="C51" s="12" t="n">
-        <v>87</v>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D51" s="12" t="n">
         <v>87</v>
       </c>
       <c r="E51" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F51" s="13" t="n">
+      <c r="G51" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8499,27 +8735,32 @@
           <t>Hoteles Solar</t>
         </is>
       </c>
-      <c r="C52" s="12" t="n">
-        <v>72</v>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D52" s="12" t="n">
         <v>72</v>
       </c>
       <c r="E52" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="G52" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8534,27 +8775,32 @@
           <t>DOT Hotels</t>
         </is>
       </c>
-      <c r="C53" s="12" t="n">
-        <v>44</v>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D53" s="12" t="n">
         <v>44</v>
       </c>
       <c r="E53" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="13" t="n">
+      <c r="G53" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8569,27 +8815,32 @@
           <t>Viaggio</t>
         </is>
       </c>
-      <c r="C54" s="12" t="n">
-        <v>42</v>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D54" s="12" t="n">
         <v>42</v>
       </c>
       <c r="E54" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F54" s="13" t="n">
+      <c r="G54" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8604,27 +8855,32 @@
           <t>Lomas Hospitality</t>
         </is>
       </c>
-      <c r="C55" s="12" t="n">
-        <v>30</v>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D55" s="12" t="n">
         <v>30</v>
       </c>
       <c r="E55" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F55" s="13" t="n">
+      <c r="G55" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8672,7 +8928,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10772,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10895,7 +11151,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13344,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13241,7 +13497,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13394,7 +13650,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13547,14 +13803,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B Opaco · BKGS&gt;0 · peor Eficacia · ordenado ↑</t>
+          <t>B2B Opaco · BKGS&gt;0 · peor Eficacia · ordenado por Eficacia ↑ (menor primero)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -15908,7 +16164,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18107,7 +18363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20274,18 +20530,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20305,7 +20562,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20322,35 +20579,40 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -20365,27 +20627,32 @@
           <t>IHG</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>379911</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>349010</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>5285</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.9186625288554424</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.01391115287527868</v>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -20400,27 +20667,32 @@
           <t>Hilton</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, HBSI, Internal</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>255301</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>247329</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>2493</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.9687741136932484</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.009764944124778203</v>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -20435,27 +20707,32 @@
           <t>Hyatt</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>157813</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>152843</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>1822</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.9685070304727748</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.01154530995545361</v>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -20470,27 +20747,32 @@
           <t>Accor</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>39908</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>37392</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.9369549964919315</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.001829207176505964</v>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -20505,27 +20787,32 @@
           <t>AA-Independent</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, HBSI, HotelBeds Apitude, Internal, Siteminder, SynXis, Travelclick</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>34220</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>31588</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>693</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.9230859146697837</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.02025131502045588</v>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -20540,27 +20827,32 @@
           <t>Caesars Entertainment</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>24282</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>19575</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.8061527057079318</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.008360102133267442</v>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -20575,27 +20867,32 @@
           <t>Wyndham</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>22743</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="E12" s="12" t="n">
         <v>21688</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.9536121004265049</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.004177109440267335</v>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -20610,27 +20907,32 @@
           <t>Marriott</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>19778</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>19449</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="G13" s="13" t="n">
         <v>0.9833653554454445</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.001820204267367782</v>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -20645,27 +20947,32 @@
           <t>MGM Resorts</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>17502</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>17218</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="G14" s="13" t="n">
         <v>0.9837732830533653</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.01342703691006742</v>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -20680,27 +20987,32 @@
           <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>11293</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>11222</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="G15" s="13" t="n">
         <v>0.9937129195076596</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.006287080492340388</v>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -20715,27 +21027,32 @@
           <t>Barcelo</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
         <v>8008</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>7254</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="G16" s="13" t="n">
         <v>0.9058441558441559</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.009365634365634366</v>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -20750,27 +21067,32 @@
           <t>Disney</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>7255</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>7171</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="G17" s="13" t="n">
         <v>0.9884217780840799</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.004824259131633356</v>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -20785,27 +21107,32 @@
           <t>Best Western</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, SynXis</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>6397</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>5927</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="G18" s="13" t="n">
         <v>0.9265280600281381</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.002970142254181648</v>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -20820,27 +21147,32 @@
           <t>Palladium Hotel Group</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
-        <v>5352</v>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D19" s="12" t="n">
         <v>5352</v>
       </c>
       <c r="E19" s="12" t="n">
+        <v>5352</v>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>262</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="G19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.04895366218236173</v>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -20855,27 +21187,32 @@
           <t>Universal</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n">
         <v>4725</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="E20" s="12" t="n">
         <v>3579</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="G20" s="13" t="n">
         <v>0.7574603174603175</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.005291005291005291</v>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -20890,27 +21227,32 @@
           <t>PAM Hotels</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Internal, SynXis</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>4116</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="E21" s="12" t="n">
         <v>4046</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="G21" s="13" t="n">
         <v>0.9829931972789115</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.01676384839650146</v>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -20925,27 +21267,32 @@
           <t>Hoteles Xcaret</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>4032</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>4020</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="G22" s="13" t="n">
         <v>0.9970238095238095</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.003472222222222222</v>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -20960,27 +21307,32 @@
           <t>Park Royal</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>3318</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="E23" s="12" t="n">
         <v>3282</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="G23" s="13" t="n">
         <v>0.9891500904159132</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.01868595539481615</v>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -20995,27 +21347,32 @@
           <t>RIU</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
-        <v>2624</v>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D24" s="12" t="n">
         <v>2624</v>
       </c>
       <c r="E24" s="12" t="n">
+        <v>2624</v>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="G24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.01333841463414634</v>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -21030,27 +21387,32 @@
           <t>Decameron</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>2570</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="E25" s="12" t="n">
         <v>2041</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="G25" s="13" t="n">
         <v>0.7941634241245136</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.04202334630350195</v>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -21065,27 +21427,32 @@
           <t>Ocean by H10</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>2298</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="E26" s="12" t="n">
         <v>2254</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="G26" s="13" t="n">
         <v>0.9808529155787642</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.01087902523933855</v>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -21100,27 +21467,32 @@
           <t>GRUPO POSADAS</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>2200</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="E27" s="12" t="n">
         <v>2128</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="G27" s="13" t="n">
         <v>0.9672727272727273</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.02318181818181818</v>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -21135,27 +21507,32 @@
           <t>Emporio</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>2189</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="E28" s="12" t="n">
         <v>2167</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="G28" s="13" t="n">
         <v>0.9899497487437185</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.02329830973047053</v>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -21170,27 +21547,32 @@
           <t>Presidente Intercontinental</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
         <v>2156</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="E29" s="12" t="n">
         <v>1913</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="G29" s="13" t="n">
         <v>0.887291280148423</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.02411873840445269</v>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -21205,27 +21587,32 @@
           <t>Melia</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
         <v>1994</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="E30" s="12" t="n">
         <v>1146</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="G30" s="13" t="n">
         <v>0.5747241725175527</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.001504513540621865</v>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -21240,27 +21627,32 @@
           <t>Krystal</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
         <v>1989</v>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="E31" s="12" t="n">
         <v>1959</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="G31" s="13" t="n">
         <v>0.9849170437405732</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.01508295625942685</v>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -21275,27 +21667,32 @@
           <t>CHOICE</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="n">
         <v>1781</v>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="E32" s="12" t="n">
         <v>1639</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="G32" s="13" t="n">
         <v>0.9202695115103874</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.002245929253228523</v>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -21310,27 +21707,32 @@
           <t>Palace</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n">
-        <v>1484</v>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D33" s="12" t="n">
         <v>1484</v>
       </c>
       <c r="E33" s="12" t="n">
+        <v>1484</v>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="G33" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.02021563342318059</v>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -21345,27 +21747,32 @@
           <t>Wynn Las Vegas</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n">
         <v>1365</v>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="E34" s="12" t="n">
         <v>1361</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="G34" s="13" t="n">
         <v>0.9970695970695971</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.008791208791208791</v>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -21380,27 +21787,32 @@
           <t>Karisma</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
         <v>1236</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="E35" s="12" t="n">
         <v>1165</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="G35" s="13" t="n">
         <v>0.9425566343042071</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.02184466019417476</v>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -21415,27 +21827,32 @@
           <t>Las Brisas</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="n">
         <v>1210</v>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="E36" s="12" t="n">
         <v>1202</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="G36" s="13" t="n">
         <v>0.9933884297520661</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.04049586776859504</v>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -21450,27 +21867,32 @@
           <t>Royalton Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="n">
         <v>1164</v>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="E37" s="12" t="n">
         <v>1102</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F37" s="13" t="n">
+      <c r="G37" s="13" t="n">
         <v>0.9467353951890034</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.003436426116838488</v>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -21485,27 +21907,32 @@
           <t>Oasis</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
-        <v>1067</v>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D38" s="12" t="n">
         <v>1067</v>
       </c>
       <c r="E38" s="12" t="n">
+        <v>1067</v>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F38" s="13" t="n">
+      <c r="G38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>0.00937207122774133</v>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -21520,27 +21947,32 @@
           <t>Bahia Principe</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
         <v>1003</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="E39" s="12" t="n">
         <v>985</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="G39" s="13" t="n">
         <v>0.9820538384845464</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.02392821535393819</v>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -21555,27 +21987,32 @@
           <t>Camino Real</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Travelclick</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="n">
         <v>901</v>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="E40" s="12" t="n">
         <v>899</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="G40" s="13" t="n">
         <v>0.9977802441731409</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.05438401775804662</v>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -21590,27 +22027,32 @@
           <t>GHL</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
         <v>876</v>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="E41" s="12" t="n">
         <v>863</v>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="G41" s="13" t="n">
         <v>0.9851598173515982</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.02625570776255708</v>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -21625,27 +22067,32 @@
           <t>Iberostar</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="n">
         <v>781</v>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="E42" s="12" t="n">
         <v>405</v>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="13" t="n">
+      <c r="G42" s="13" t="n">
         <v>0.5185659411011524</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.001280409731113956</v>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -21660,27 +22107,32 @@
           <t>Hoteles Geh Suites</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>758</v>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="E43" s="12" t="n">
         <v>735</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="G43" s="13" t="n">
         <v>0.9696569920844327</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0.01978891820580475</v>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -21695,27 +22147,32 @@
           <t>Dann</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="n">
         <v>652</v>
       </c>
-      <c r="D44" s="12" t="n">
+      <c r="E44" s="12" t="n">
         <v>648</v>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="13" t="n">
+      <c r="G44" s="13" t="n">
         <v>0.9938650306748467</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.001533742331288344</v>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -21730,27 +22187,32 @@
           <t>Americas Hotels Group</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
         <v>636</v>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="E45" s="12" t="n">
         <v>597</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F45" s="13" t="n">
+      <c r="G45" s="13" t="n">
         <v>0.9386792452830188</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.02987421383647799</v>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -21765,27 +22227,32 @@
           <t>Sandos</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n">
-        <v>489</v>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D46" s="12" t="n">
         <v>489</v>
       </c>
       <c r="E46" s="12" t="n">
+        <v>489</v>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="13" t="n">
+      <c r="G46" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -21800,27 +22267,32 @@
           <t>Pueblo Bonito</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n">
-        <v>337</v>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D47" s="12" t="n">
         <v>337</v>
       </c>
       <c r="E47" s="12" t="n">
+        <v>337</v>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F47" s="13" t="n">
+      <c r="G47" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.03264094955489615</v>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -21835,27 +22307,32 @@
           <t>El Dorado San Andrés</t>
         </is>
       </c>
-      <c r="C48" s="12" t="n">
-        <v>308</v>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D48" s="12" t="n">
         <v>308</v>
       </c>
       <c r="E48" s="12" t="n">
+        <v>308</v>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="G48" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0.01948051948051948</v>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -21870,27 +22347,32 @@
           <t>EM Hotels</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n">
-        <v>303</v>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D49" s="12" t="n">
         <v>303</v>
       </c>
       <c r="E49" s="12" t="n">
+        <v>303</v>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="13" t="n">
+      <c r="G49" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -21905,27 +22387,32 @@
           <t>Villa Group</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
-        <v>300</v>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D50" s="12" t="n">
         <v>300</v>
       </c>
       <c r="E50" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="G50" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.02</v>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -21940,27 +22427,32 @@
           <t>Hoteles Solar</t>
         </is>
       </c>
-      <c r="C51" s="12" t="n">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="n">
         <v>289</v>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="E51" s="12" t="n">
         <v>288</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F51" s="13" t="n">
+      <c r="G51" s="13" t="n">
         <v>0.9965397923875432</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.03806228373702422</v>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -21975,27 +22467,32 @@
           <t>Faranda Hotels</t>
         </is>
       </c>
-      <c r="C52" s="12" t="n">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="D52" s="12" t="n">
+      <c r="E52" s="12" t="n">
         <v>268</v>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="G52" s="13" t="n">
         <v>0.9962825278810409</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0.003717472118959108</v>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -22010,27 +22507,32 @@
           <t>Dorado Plaza</t>
         </is>
       </c>
-      <c r="C53" s="12" t="n">
-        <v>246</v>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D53" s="12" t="n">
         <v>246</v>
       </c>
       <c r="E53" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="13" t="n">
+      <c r="G53" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -22045,27 +22547,32 @@
           <t>Station Casinos</t>
         </is>
       </c>
-      <c r="C54" s="12" t="n">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="n">
         <v>233</v>
-      </c>
-      <c r="D54" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F54" s="13" t="n">
+      <c r="F54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="H54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -22080,27 +22587,32 @@
           <t>BH Hoteles</t>
         </is>
       </c>
-      <c r="C55" s="12" t="n">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="n">
         <v>211</v>
       </c>
-      <c r="D55" s="12" t="n">
+      <c r="E55" s="12" t="n">
         <v>210</v>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F55" s="13" t="n">
+      <c r="G55" s="13" t="n">
         <v>0.995260663507109</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.01895734597156398</v>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -22148,7 +22660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23992,7 +24504,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24491,7 +25003,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -26684,7 +27196,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -26837,14 +27349,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hoteles del P80 con BKGS&gt;0 · peor Eficacia · ordenado por Eficacia ↑</t>
+          <t>Hoteles del P80 con BKGS&gt;0 · peor Eficacia · ordenado por Eficacia ↑ (menor primero)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29192,7 +29704,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29345,14 +29857,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG · BKGS&gt;0 · peor Eficacia · ordenado ↑</t>
+          <t>CUG · BKGS&gt;0 · peor Eficacia · ordenado por Eficacia ↑ (menor primero)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -31706,7 +32218,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33905,7 +34417,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -36072,18 +36584,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36103,7 +36616,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -36120,35 +36633,40 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -36163,27 +36681,32 @@
           <t>IHG</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>140363</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>126838</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>4247</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.9036426978619722</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.03025726152903543</v>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -36198,27 +36721,32 @@
           <t>Hilton</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, HBSI, HotelBeds Apitude, Internal</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>72144</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>70079</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>1098</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.9713766910623198</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.01521956087824351</v>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -36233,27 +36761,32 @@
           <t>Hyatt</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>54779</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>52885</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>970</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.9654247065481297</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.01770751565380894</v>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -36268,27 +36801,32 @@
           <t>AA-Independent</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, HBSI, HotelBeds Apitude, Internal, Omnibees, Siteminder, SynXis, Travelclick</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>24919</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>23416</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>970</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.9396845780328263</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.03892612063084393</v>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -36303,27 +36841,32 @@
           <t>Accor</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>20113</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>18762</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.9328295132501367</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.0045741560184955</v>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -36338,27 +36881,32 @@
           <t>Marriott</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Expedia, HotelBeds Apitude, Internal</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>10773</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>10017</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.9298245614035088</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.002970388935301216</v>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -36373,27 +36921,32 @@
           <t>Wyndham</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>6795</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="E12" s="12" t="n">
         <v>6381</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>206</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.9390728476821192</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.03031640912435615</v>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -36408,27 +36961,32 @@
           <t>Caesars Entertainment</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>6347</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>5192</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="G13" s="13" t="n">
         <v>0.8180242634315424</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.01953678903418938</v>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -36443,27 +37001,32 @@
           <t>Barcelo</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>5604</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>4930</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="G14" s="13" t="n">
         <v>0.8797287651677373</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.03783012134189864</v>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -36478,27 +37041,32 @@
           <t>MGM Resorts</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>5561</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>5444</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="G15" s="13" t="n">
         <v>0.9789606185937781</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.02625427081460169</v>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -36513,27 +37081,32 @@
           <t>CHOICE</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
         <v>4094</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>3982</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="G16" s="13" t="n">
         <v>0.9726428920371275</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.007327796775769418</v>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -36548,27 +37121,32 @@
           <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>3578</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>3569</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="G17" s="13" t="n">
         <v>0.9974846282839576</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.01956400223588597</v>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -36583,27 +37161,32 @@
           <t>Best Western</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, SynXis</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>3526</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>2985</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="G18" s="13" t="n">
         <v>0.8465683494044243</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.004254112308564946</v>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -36618,27 +37201,32 @@
           <t>Universal</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
         <v>3320</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="E19" s="12" t="n">
         <v>2521</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="G19" s="13" t="n">
         <v>0.7593373493975903</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.007228915662650603</v>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -36653,27 +37241,32 @@
           <t>Palladium Hotel Group</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
-        <v>3030</v>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D20" s="12" t="n">
         <v>3030</v>
       </c>
       <c r="E20" s="12" t="n">
+        <v>3030</v>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>253</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="G20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.0834983498349835</v>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -36688,27 +37281,32 @@
           <t>RIU</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>2847</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="E21" s="12" t="n">
         <v>2833</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="G21" s="13" t="n">
         <v>0.9950825430277485</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.03582718651211802</v>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -36723,27 +37321,32 @@
           <t>Bahia Principe</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>2599</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>2555</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>145</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="G22" s="13" t="n">
         <v>0.9830704116968064</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.05579068872643324</v>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -36758,27 +37361,32 @@
           <t>Disney</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>2592</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="E23" s="12" t="n">
         <v>2545</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="G23" s="13" t="n">
         <v>0.9818672839506173</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.006172839506172839</v>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -36793,27 +37401,32 @@
           <t>Decameron</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>2592</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="E24" s="12" t="n">
         <v>2346</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="G24" s="13" t="n">
         <v>0.9050925925925926</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.01350308641975309</v>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -36828,27 +37441,32 @@
           <t>Hoteles Xcaret</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>2526</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="E25" s="12" t="n">
         <v>2518</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="G25" s="13" t="n">
         <v>0.9968329374505146</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.007521773555027712</v>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -36863,27 +37481,32 @@
           <t>Park Royal</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>2230</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="E26" s="12" t="n">
         <v>2194</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="G26" s="13" t="n">
         <v>0.9838565022421525</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.02600896860986547</v>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -36898,27 +37521,32 @@
           <t>GRUPO POSADAS</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>2227</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="E27" s="12" t="n">
         <v>2096</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="G27" s="13" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.06645711719802425</v>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -36933,27 +37561,32 @@
           <t>Ocean by H10</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>1806</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="E28" s="12" t="n">
         <v>1780</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="G28" s="13" t="n">
         <v>0.9856035437430787</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.08139534883720931</v>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -36968,27 +37601,32 @@
           <t>PAM Hotels</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Internal, SynXis</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
         <v>1518</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="E29" s="12" t="n">
         <v>1468</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="G29" s="13" t="n">
         <v>0.9670619235836627</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.05599472990777338</v>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37003,27 +37641,32 @@
           <t>Krystal</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
         <v>1505</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="E30" s="12" t="n">
         <v>1439</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="G30" s="13" t="n">
         <v>0.9561461794019933</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.03056478405315615</v>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37038,27 +37681,32 @@
           <t>Emporio</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
         <v>1469</v>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="E31" s="12" t="n">
         <v>1444</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="G31" s="13" t="n">
         <v>0.9829816201497618</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.03539823008849557</v>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37073,27 +37721,32 @@
           <t>Las Brisas</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="n">
         <v>1442</v>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="E32" s="12" t="n">
         <v>1431</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="G32" s="13" t="n">
         <v>0.992371705963939</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.07212205270457697</v>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37108,27 +37761,32 @@
           <t>Melia</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n">
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n">
         <v>1323</v>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="E33" s="12" t="n">
         <v>718</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="G33" s="13" t="n">
         <v>0.5427059712773998</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.01360544217687075</v>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -37143,27 +37801,32 @@
           <t>Iberostar</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>HBSI, Internal</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n">
         <v>1290</v>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="E34" s="12" t="n">
         <v>447</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="G34" s="13" t="n">
         <v>0.3465116279069768</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.004651162790697674</v>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -37178,27 +37841,32 @@
           <t>Royalton Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
         <v>1178</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="E35" s="12" t="n">
         <v>1112</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="G35" s="13" t="n">
         <v>0.9439728353140917</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.03904923599320883</v>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37213,27 +37881,32 @@
           <t>Palace</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
-        <v>1004</v>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D36" s="12" t="n">
         <v>1004</v>
       </c>
       <c r="E36" s="12" t="n">
+        <v>1004</v>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="G36" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.02191235059760956</v>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -37248,27 +37921,32 @@
           <t>Oasis</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="n">
         <v>965</v>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="E37" s="12" t="n">
         <v>959</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F37" s="13" t="n">
+      <c r="G37" s="13" t="n">
         <v>0.9937823834196892</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.00932642487046632</v>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -37283,27 +37961,32 @@
           <t>Presidente Intercontinental</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>773</v>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="E38" s="12" t="n">
         <v>670</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="F38" s="13" t="n">
+      <c r="G38" s="13" t="n">
         <v>0.8667529107373868</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>0.05692108667529108</v>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37318,27 +38001,32 @@
           <t>Karisma</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
         <v>736</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="E39" s="12" t="n">
         <v>707</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="G39" s="13" t="n">
         <v>0.9605978260869565</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.03940217391304348</v>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37353,27 +38041,32 @@
           <t>Wynn Las Vegas</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
-        <v>609</v>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
       </c>
       <c r="D40" s="12" t="n">
         <v>609</v>
       </c>
       <c r="E40" s="12" t="n">
+        <v>609</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="G40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.01149425287356322</v>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -37388,27 +38081,32 @@
           <t>Camino Real</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Travelclick</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="E41" s="12" t="n">
         <v>521</v>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="G41" s="13" t="n">
         <v>0.9923809523809524</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.06095238095238095</v>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37423,27 +38121,32 @@
           <t>Hoteles Geh Suites</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="n">
         <v>502</v>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="E42" s="12" t="n">
         <v>490</v>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F42" s="13" t="n">
+      <c r="G42" s="13" t="n">
         <v>0.9760956175298805</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.01593625498007968</v>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -37458,27 +38161,32 @@
           <t>El Dorado San Andrés</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>391</v>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="E43" s="12" t="n">
         <v>390</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="G43" s="13" t="n">
         <v>0.9974424552429667</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -37493,27 +38201,32 @@
           <t>GHL</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
-        <v>378</v>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D44" s="12" t="n">
         <v>378</v>
       </c>
       <c r="E44" s="12" t="n">
+        <v>378</v>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F44" s="13" t="n">
+      <c r="G44" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.05291005291005291</v>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37528,27 +38241,32 @@
           <t>Dann</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
         <v>316</v>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="E45" s="12" t="n">
         <v>313</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F45" s="13" t="n">
+      <c r="G45" s="13" t="n">
         <v>0.990506329113924</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.02531645569620253</v>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37563,27 +38281,32 @@
           <t>Hoteles Solar</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="n">
         <v>295</v>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="E46" s="12" t="n">
         <v>294</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F46" s="13" t="n">
+      <c r="G46" s="13" t="n">
         <v>0.9966101694915255</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.0711864406779661</v>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37598,27 +38321,32 @@
           <t>Sandos</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n">
-        <v>195</v>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D47" s="12" t="n">
         <v>195</v>
       </c>
       <c r="E47" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="13" t="n">
+      <c r="G47" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.01025641025641026</v>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -37633,27 +38361,32 @@
           <t>Pueblo Bonito</t>
         </is>
       </c>
-      <c r="C48" s="12" t="n">
-        <v>188</v>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D48" s="12" t="n">
         <v>188</v>
       </c>
       <c r="E48" s="12" t="n">
+        <v>188</v>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="G48" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0.03723404255319149</v>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37668,27 +38401,32 @@
           <t>Americas Hotels Group</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="n">
         <v>167</v>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="E49" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F49" s="13" t="n">
+      <c r="G49" s="13" t="n">
         <v>0.9760479041916168</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0.05389221556886228</v>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -37703,27 +38441,32 @@
           <t>Faranda Hotels</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
-        <v>128</v>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D50" s="12" t="n">
         <v>128</v>
       </c>
       <c r="E50" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="G50" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.015625</v>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -37738,27 +38481,32 @@
           <t>NH</t>
         </is>
       </c>
-      <c r="C51" s="12" t="n">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>HotelBeds Apitude, Internal</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="E51" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="13" t="n">
+      <c r="G51" s="13" t="n">
         <v>0.528</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.008</v>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -37773,27 +38521,32 @@
           <t>Station Casinos</t>
         </is>
       </c>
-      <c r="C52" s="12" t="n">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="D52" s="12" t="n">
+      <c r="E52" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="G52" s="13" t="n">
         <v>0.1842105263157895</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -37808,27 +38561,32 @@
           <t>EM Hotels</t>
         </is>
       </c>
-      <c r="C53" s="12" t="n">
-        <v>106</v>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D53" s="12" t="n">
         <v>106</v>
       </c>
       <c r="E53" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="13" t="n">
+      <c r="G53" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0.01886792452830189</v>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -37843,27 +38601,32 @@
           <t>Dorado Plaza</t>
         </is>
       </c>
-      <c r="C54" s="12" t="n">
-        <v>99</v>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D54" s="12" t="n">
         <v>99</v>
       </c>
       <c r="E54" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F54" s="13" t="n">
+      <c r="G54" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -37878,27 +38641,32 @@
           <t>Villa Group</t>
         </is>
       </c>
-      <c r="C55" s="12" t="n">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="D55" s="12" t="n">
+      <c r="E55" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="13" t="n">
+      <c r="G55" s="13" t="n">
         <v>0.9891304347826086</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.0108695652173913</v>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -37946,7 +38714,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -39790,7 +40558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40289,7 +41057,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42488,7 +43256,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44686,7 +45454,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -46698,18 +47466,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -46729,7 +47498,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -46746,35 +47515,40 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -46789,27 +47563,32 @@
           <t>IHG</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>564222</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>519643</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>9135</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.9209903194132806</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.01619043567957294</v>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -46824,27 +47603,32 @@
           <t>Hilton</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, HBSI, Internal</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>405244</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>388383</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>3618</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.9583929681870675</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.008927954516291419</v>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -46859,27 +47643,32 @@
           <t>Hyatt</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>264047</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>254742</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>2926</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.9647600616556901</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.0110813605153628</v>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -46894,27 +47683,32 @@
           <t>AA-Independent</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, HBSI, HotelBeds Apitude, Internal, Omnibees, Siteminder, SynXis, Travelclick</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>80786</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>75281</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>2115</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.9318570049265962</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.02618027876117149</v>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -46929,27 +47723,32 @@
           <t>Accor</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>72514</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>68045</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.9383705215544584</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.002454698403066994</v>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -46964,27 +47763,32 @@
           <t>Wyndham</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>40387</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>38287</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>311</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.9480030702948968</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.007700497684898606</v>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -46999,27 +47803,32 @@
           <t>Caesars Entertainment</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>39023</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="E12" s="12" t="n">
         <v>31063</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>351</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.7960177331317428</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.008994695436024908</v>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -47034,27 +47843,32 @@
           <t>MGM Resorts</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>26121</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>25630</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>383</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="G13" s="13" t="n">
         <v>0.9812028635963401</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.01466253206232533</v>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -47069,27 +47883,32 @@
           <t>Marriott</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>25572</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>24546</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="G14" s="13" t="n">
         <v>0.9598779915532614</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.002541842640387924</v>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -47104,27 +47923,32 @@
           <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>19504</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>19418</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>145</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="G15" s="13" t="n">
         <v>0.9955906480721903</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.007434372436423298</v>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -47139,27 +47963,32 @@
           <t>Barcelo</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
         <v>15328</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>13857</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>289</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="G16" s="13" t="n">
         <v>0.9040318371607515</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.01885438413361169</v>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -47174,27 +48003,32 @@
           <t>Disney</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>13461</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>13292</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="G17" s="13" t="n">
         <v>0.987445212094198</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.006463115667483842</v>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -47209,27 +48043,32 @@
           <t>Best Western</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, SynXis</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>11265</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>10444</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="G18" s="13" t="n">
         <v>0.9271193963604083</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.002663115845539281</v>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -47244,27 +48083,32 @@
           <t>Universal</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
         <v>10165</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="E19" s="12" t="n">
         <v>7784</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="G19" s="13" t="n">
         <v>0.7657648794884407</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.006099360550909985</v>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -47279,27 +48123,32 @@
           <t>Palladium Hotel Group</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
-        <v>8855</v>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D20" s="12" t="n">
         <v>8855</v>
       </c>
       <c r="E20" s="12" t="n">
+        <v>8855</v>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>526</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="G20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.05940146809712027</v>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -47314,27 +48163,32 @@
           <t>Hoteles Xcaret</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>6872</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="E21" s="12" t="n">
         <v>6852</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="G21" s="13" t="n">
         <v>0.9970896391152503</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.00480209545983702</v>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -47349,27 +48203,32 @@
           <t>PAM Hotels</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Internal, SynXis</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>6545</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>6413</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="G22" s="13" t="n">
         <v>0.9798319327731092</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.02352941176470588</v>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -47384,27 +48243,32 @@
           <t>Park Royal</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>6100</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="E23" s="12" t="n">
         <v>6019</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="G23" s="13" t="n">
         <v>0.9867213114754099</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.02016393442622951</v>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -47419,27 +48283,32 @@
           <t>Decameron</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>6071</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="E24" s="12" t="n">
         <v>5197</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="G24" s="13" t="n">
         <v>0.8560368967221216</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.024378191401746</v>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -47454,27 +48323,32 @@
           <t>RIU</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>5351</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="E25" s="12" t="n">
         <v>5341</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>144</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="G25" s="13" t="n">
         <v>0.998131190431695</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.02691085778359185</v>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -47489,27 +48363,32 @@
           <t>CHOICE</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>5225</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="E26" s="12" t="n">
         <v>4949</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="G26" s="13" t="n">
         <v>0.947177033492823</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.004593301435406699</v>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -47524,27 +48403,32 @@
           <t>GRUPO POSADAS</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>4514</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="E27" s="12" t="n">
         <v>4318</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="G27" s="13" t="n">
         <v>0.9565795303500222</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.02747009304386354</v>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -47559,27 +48443,32 @@
           <t>Ocean by H10</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>4463</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="E28" s="12" t="n">
         <v>4390</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="G28" s="13" t="n">
         <v>0.983643289267309</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.0398834864440959</v>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -47594,27 +48483,32 @@
           <t>Emporio</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
         <v>4101</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="E29" s="12" t="n">
         <v>4052</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="G29" s="13" t="n">
         <v>0.9880516947086077</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.02511582540843697</v>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -47629,27 +48523,32 @@
           <t>Bahia Principe</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
         <v>4021</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="E30" s="12" t="n">
         <v>3937</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="G30" s="13" t="n">
         <v>0.9791096742103954</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.04227804028848545</v>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -47664,27 +48563,32 @@
           <t>Presidente Intercontinental</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
         <v>3794</v>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="E31" s="12" t="n">
         <v>3320</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="G31" s="13" t="n">
         <v>0.875065893516078</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.02556668423827095</v>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -47699,27 +48603,32 @@
           <t>Krystal</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="n">
         <v>3654</v>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="E32" s="12" t="n">
         <v>3384</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="G32" s="13" t="n">
         <v>0.9261083743842364</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.01915708812260536</v>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -47734,27 +48643,32 @@
           <t>Melia</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n">
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n">
         <v>3506</v>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="E33" s="12" t="n">
         <v>1739</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="G33" s="13" t="n">
         <v>0.4960068454078722</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.004848830576155163</v>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -47769,27 +48683,32 @@
           <t>Wynn Las Vegas</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n">
         <v>2727</v>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="E34" s="12" t="n">
         <v>2721</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="G34" s="13" t="n">
         <v>0.9977997799779978</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.0088008800880088</v>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -47804,27 +48723,32 @@
           <t>Oasis</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
         <v>2689</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="E35" s="12" t="n">
         <v>2683</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="G35" s="13" t="n">
         <v>0.9977686872443288</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.007809594644849386</v>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -47839,27 +48763,32 @@
           <t>Las Brisas</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="n">
         <v>2679</v>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="E36" s="12" t="n">
         <v>2660</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="G36" s="13" t="n">
         <v>0.9929078014184397</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.05225830533781262</v>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -47874,27 +48803,32 @@
           <t>Iberostar</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>HBSI, Internal</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="n">
         <v>2548</v>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="E37" s="12" t="n">
         <v>1175</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F37" s="13" t="n">
+      <c r="G37" s="13" t="n">
         <v>0.4611459968602826</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.00706436420722135</v>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -47909,27 +48843,32 @@
           <t>Royalton Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>2444</v>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="E38" s="12" t="n">
         <v>2317</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F38" s="13" t="n">
+      <c r="G38" s="13" t="n">
         <v>0.9480360065466449</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>0.02086743044189853</v>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -47944,27 +48883,32 @@
           <t>Camino Real</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Travelclick</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
         <v>2420</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="E39" s="12" t="n">
         <v>2413</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="G39" s="13" t="n">
         <v>0.9971074380165289</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.06570247933884298</v>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -47979,27 +48923,32 @@
           <t>Palace</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
-        <v>2401</v>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D40" s="12" t="n">
         <v>2401</v>
       </c>
       <c r="E40" s="12" t="n">
+        <v>2401</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="G40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.0212411495210329</v>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -48014,27 +48963,32 @@
           <t>Karisma</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
         <v>2338</v>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="E41" s="12" t="n">
         <v>2220</v>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="G41" s="13" t="n">
         <v>0.9495295124037639</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.02480752780153978</v>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -48049,27 +49003,32 @@
           <t>Hoteles Geh Suites</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="n">
         <v>1920</v>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="E42" s="12" t="n">
         <v>1862</v>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F42" s="13" t="n">
+      <c r="G42" s="13" t="n">
         <v>0.9697916666666667</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.01510416666666667</v>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -48084,27 +49043,32 @@
           <t>GHL</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>1593</v>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="E43" s="12" t="n">
         <v>1580</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="G43" s="13" t="n">
         <v>0.9918392969240427</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0.03138731952291274</v>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -48119,27 +49083,32 @@
           <t>Dann</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="n">
         <v>1378</v>
       </c>
-      <c r="D44" s="12" t="n">
+      <c r="E44" s="12" t="n">
         <v>1371</v>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F44" s="13" t="n">
+      <c r="G44" s="13" t="n">
         <v>0.9949201741654572</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.006531204644412192</v>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -48154,27 +49123,32 @@
           <t>Americas Hotels Group</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
         <v>1284</v>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="E45" s="12" t="n">
         <v>1225</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="F45" s="13" t="n">
+      <c r="G45" s="13" t="n">
         <v>0.9540498442367601</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.03504672897196261</v>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -48189,27 +49163,32 @@
           <t>Sandos</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n">
-        <v>958</v>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D46" s="12" t="n">
         <v>958</v>
       </c>
       <c r="E46" s="12" t="n">
+        <v>958</v>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="13" t="n">
+      <c r="G46" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.00208768267223382</v>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -48224,27 +49203,32 @@
           <t>Mision</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n">
-        <v>821</v>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D47" s="12" t="n">
         <v>821</v>
       </c>
       <c r="E47" s="12" t="n">
+        <v>821</v>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="F47" s="13" t="n">
+      <c r="G47" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.06090133982947625</v>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -48259,27 +49243,32 @@
           <t>EM Hotels</t>
         </is>
       </c>
-      <c r="C48" s="12" t="n">
-        <v>757</v>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D48" s="12" t="n">
         <v>757</v>
       </c>
       <c r="E48" s="12" t="n">
+        <v>757</v>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="G48" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0.003963011889035667</v>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -48294,27 +49283,32 @@
           <t>Hoteles Solar</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="n">
         <v>714</v>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="E49" s="12" t="n">
         <v>712</v>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F49" s="13" t="n">
+      <c r="G49" s="13" t="n">
         <v>0.9971988795518207</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0.05602240896358544</v>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -48329,27 +49323,32 @@
           <t>Faranda Hotels</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="n">
         <v>637</v>
       </c>
-      <c r="D50" s="12" t="n">
+      <c r="E50" s="12" t="n">
         <v>633</v>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="G50" s="13" t="n">
         <v>0.9937205651491365</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.007849293563579277</v>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -48364,27 +49363,32 @@
           <t>El Dorado San Andrés</t>
         </is>
       </c>
-      <c r="C51" s="12" t="n">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="n">
         <v>628</v>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="E51" s="12" t="n">
         <v>627</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F51" s="13" t="n">
+      <c r="G51" s="13" t="n">
         <v>0.9984076433121019</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.009554140127388535</v>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -48399,27 +49403,32 @@
           <t>Hoteles Movich</t>
         </is>
       </c>
-      <c r="C52" s="12" t="n">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="n">
         <v>627</v>
       </c>
-      <c r="D52" s="12" t="n">
+      <c r="E52" s="12" t="n">
         <v>625</v>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="G52" s="13" t="n">
         <v>0.9968102073365231</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0.03827751196172249</v>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -48434,27 +49443,32 @@
           <t>Dorado Plaza</t>
         </is>
       </c>
-      <c r="C53" s="12" t="n">
-        <v>578</v>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D53" s="12" t="n">
         <v>578</v>
       </c>
       <c r="E53" s="12" t="n">
+        <v>578</v>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="13" t="n">
+      <c r="G53" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0.003460207612456748</v>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -48469,27 +49483,32 @@
           <t>Pueblo Bonito</t>
         </is>
       </c>
-      <c r="C54" s="12" t="n">
-        <v>525</v>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D54" s="12" t="n">
         <v>525</v>
       </c>
       <c r="E54" s="12" t="n">
+        <v>525</v>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F54" s="13" t="n">
+      <c r="G54" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>0.03428571428571429</v>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -48504,27 +49523,32 @@
           <t>Oxo Hotel</t>
         </is>
       </c>
-      <c r="C55" s="12" t="n">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="n">
         <v>486</v>
       </c>
-      <c r="D55" s="12" t="n">
+      <c r="E55" s="12" t="n">
         <v>483</v>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F55" s="13" t="n">
+      <c r="G55" s="13" t="n">
         <v>0.9938271604938271</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.02674897119341564</v>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -48572,7 +49596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -50416,7 +51440,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -50915,7 +51939,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-19/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-19/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="43" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -2408,7 +2408,7 @@
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
@@ -2432,7 +2432,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -4607,7 +4607,7 @@
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -4631,7 +4631,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -6804,7 +6804,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
@@ -6830,7 +6830,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -8902,7 +8902,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -8928,7 +8928,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8945,7 +8945,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -10746,7 +10746,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -10772,7 +10772,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -11127,7 +11127,7 @@
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
@@ -11151,7 +11151,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -13344,7 +13344,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13497,7 +13497,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13650,7 +13650,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13785,7 +13785,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -13810,7 +13810,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -16140,7 +16140,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
@@ -16164,7 +16164,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16196,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -18339,7 +18339,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -18363,7 +18363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18395,7 +18395,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -20536,7 +20536,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -20562,7 +20562,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -20604,7 +20604,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -22634,7 +22634,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -22660,7 +22660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -24478,7 +24478,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -24504,7 +24504,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24526,7 +24526,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -24546,7 +24546,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -24979,7 +24979,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
@@ -25003,7 +25003,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -25035,7 +25035,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -25050,7 +25050,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -27331,7 +27331,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -27356,7 +27356,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -27388,7 +27388,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -27408,7 +27408,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -29704,7 +29704,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29839,7 +29839,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -29864,7 +29864,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -32194,7 +32194,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
@@ -32218,7 +32218,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -32250,7 +32250,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -32265,7 +32265,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -34393,7 +34393,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="43" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -34417,7 +34417,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -34449,7 +34449,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -36590,7 +36590,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -36616,7 +36616,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -36638,7 +36638,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -36658,7 +36658,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -38688,7 +38688,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -38714,7 +38714,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38731,7 +38731,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -38751,7 +38751,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -40532,7 +40532,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -40558,7 +40558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40580,7 +40580,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -40600,7 +40600,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -41033,7 +41033,7 @@
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
@@ -41057,7 +41057,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41089,7 +41089,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -41104,7 +41104,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -43232,7 +43232,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
@@ -43256,7 +43256,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -43288,7 +43288,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -43303,7 +43303,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -45431,7 +45431,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -45454,7 +45454,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45486,7 +45486,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -47472,7 +47472,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -47498,7 +47498,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47520,7 +47520,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -47540,7 +47540,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -49571,7 +49571,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
@@ -49596,7 +49596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -49618,7 +49618,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -49633,7 +49633,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -51414,7 +51414,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -51440,7 +51440,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -51462,7 +51462,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -51482,7 +51482,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -51915,7 +51915,7 @@
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
@@ -51939,7 +51939,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -51971,7 +51971,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -51986,7 +51986,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
